--- a/Candle Catalogue.xlsx
+++ b/Candle Catalogue.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\hem-catalogue-app\hem-catalogue-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C92576E-F0E5-4C53-A27F-DD7A11FEB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7704B9A-E176-4398-A8FD-046008155FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$30</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
   <si>
     <t>Category</t>
   </si>
@@ -89,9 +92,6 @@
     <t>Smudge Tea light Candle Sandalwood</t>
   </si>
   <si>
-    <t>7 CHAKRA SMUDGE TEA LIGHT FRAGRANCE CANDLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">7 Chakra Smudge Tea light Fragrance Candle </t>
   </si>
   <si>
@@ -113,9 +113,6 @@
     <t xml:space="preserve">Seven Chakra 7 in 1 unsencted Candle </t>
   </si>
   <si>
-    <t xml:space="preserve">Spell Candle pack of 20 N </t>
-  </si>
-  <si>
     <t>Spell Candle</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>7 in 1 Seven Chakras Unscented Candle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 chakra</t>
   </si>
 </sst>
 </file>
@@ -195,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[&gt;=10000000]##\,##\,##\,##0.00;[&gt;=100000]##\,##\,##0.00;##,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +219,12 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -557,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.54296875" style="2" bestFit="1" customWidth="1"/>
@@ -587,346 +593,330 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>22</v>
+      <c r="A28" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>22</v>
+      <c r="A29" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>22</v>
+      <c r="A30" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E30" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E30">
+      <sortCondition ref="A1:A30"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Candle Catalogue.xlsx
+++ b/Candle Catalogue.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30C0E4F-4959-4EAA-8717-77D3A694BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3491F577-6506-4C1E-BFA5-A247BA53BCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t xml:space="preserve">SMC - Smudge Candle Patchouli </t>
   </si>
   <si>
-    <t xml:space="preserve">Manifestation Candles </t>
-  </si>
-  <si>
     <t xml:space="preserve">7 days 7 chakra Unscented Candle </t>
   </si>
   <si>
@@ -189,6 +186,9 @@
   </si>
   <si>
     <t>SMC - Smudge Candle Patchouli 90 gms</t>
+  </si>
+  <si>
+    <t>Manifestation Candle</t>
   </si>
 </sst>
 </file>
@@ -596,35 +596,35 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -668,7 +668,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -679,73 +679,73 @@
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -753,7 +753,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>6</v>
@@ -764,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
@@ -775,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -786,10 +786,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -797,10 +797,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -808,10 +808,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -822,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -844,62 +844,62 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D25" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
